--- a/data/exams/chemistry/Chemistry2022LegacyMetadata.xlsx
+++ b/data/exams/chemistry/Chemistry2022LegacyMetadata.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\Exam\data\exams\chemistry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7034E4F2-CB1E-4A68-AA70-0196EB3730ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{721D11E8-A8B8-49B8-8A98-0CC16F042409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{76F0E50B-E87B-4DFF-B825-2EFCA8467F5E}"/>
+    <workbookView xWindow="1215" yWindow="720" windowWidth="24270" windowHeight="14175" xr2:uid="{F1B4D799-B247-4A2E-B051-5B46CF41DD52}"/>
   </bookViews>
   <sheets>
-    <sheet name="QCAA" sheetId="1" r:id="rId1"/>
+    <sheet name="2022 QCAA" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="62">
   <si>
     <t>Year</t>
   </si>
@@ -56,15 +56,33 @@
     <t>Topic</t>
   </si>
   <si>
+    <t>Answer</t>
+  </si>
+  <si>
+    <t>Preamble</t>
+  </si>
+  <si>
+    <t>MCQ</t>
+  </si>
+  <si>
     <t>4.1.3</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>4.1.1</t>
   </si>
   <si>
+    <t>D</t>
+  </si>
+  <si>
     <t>3.2.1</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>4.1.4</t>
   </si>
   <si>
@@ -81,6 +99,9 @@
   </si>
   <si>
     <t>3.1.7</t>
+  </si>
+  <si>
+    <t>C</t>
   </si>
   <si>
     <t>4.1.5</t>
@@ -320,7 +341,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{CD2F5263-410A-4FEB-AD50-BEC8C799EF8F}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{86A2004C-F13B-41CF-8118-5073381502C1}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -631,16 +652,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6EE892A-783A-42D0-91BF-CD7A0F6502DF}">
-  <dimension ref="A1:E54"/>
-  <sheetFormatPr defaultColWidth="9.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29F8849C-08B8-4D8B-98BC-EEA26B79AF0C}">
+  <dimension ref="A1:G54"/>
+  <sheetFormatPr defaultColWidth="9.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" style="2"/>
-    <col min="2" max="5" width="9.5546875" style="1"/>
-    <col min="6" max="16384" width="9.5546875" style="2"/>
+    <col min="1" max="1" width="9.85546875" style="2"/>
+    <col min="2" max="5" width="9.85546875" style="1"/>
+    <col min="6" max="16384" width="9.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -656,13 +677,19 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2022</v>
       </c>
-      <c r="B2" s="1">
-        <v>1</v>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
@@ -671,15 +698,18 @@
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2022</v>
       </c>
-      <c r="B3" s="1">
-        <v>1</v>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C3" s="1">
         <v>2</v>
@@ -688,15 +718,18 @@
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2022</v>
       </c>
-      <c r="B4" s="1">
-        <v>1</v>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
@@ -705,15 +738,18 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2022</v>
       </c>
-      <c r="B5" s="1">
-        <v>1</v>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -722,15 +758,18 @@
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2022</v>
       </c>
-      <c r="B6" s="1">
-        <v>1</v>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C6" s="1">
         <v>5</v>
@@ -739,15 +778,18 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2022</v>
       </c>
-      <c r="B7" s="1">
-        <v>1</v>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C7" s="1">
         <v>6</v>
@@ -756,15 +798,18 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2022</v>
       </c>
-      <c r="B8" s="1">
-        <v>1</v>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C8" s="1">
         <v>7</v>
@@ -773,15 +818,18 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2022</v>
       </c>
-      <c r="B9" s="1">
-        <v>1</v>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C9" s="1">
         <v>8</v>
@@ -790,15 +838,18 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2022</v>
       </c>
-      <c r="B10" s="1">
-        <v>1</v>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C10" s="1">
         <v>9</v>
@@ -807,15 +858,18 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2022</v>
       </c>
-      <c r="B11" s="1">
-        <v>1</v>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C11" s="1">
         <v>10</v>
@@ -824,15 +878,18 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2022</v>
       </c>
-      <c r="B12" s="1">
-        <v>1</v>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C12" s="1">
         <v>11</v>
@@ -841,15 +898,18 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>2022</v>
       </c>
-      <c r="B13" s="1">
-        <v>1</v>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C13" s="1">
         <v>12</v>
@@ -858,15 +918,18 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2022</v>
       </c>
-      <c r="B14" s="1">
-        <v>1</v>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C14" s="1">
         <v>13</v>
@@ -875,15 +938,18 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2022</v>
       </c>
-      <c r="B15" s="1">
-        <v>1</v>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C15" s="1">
         <v>14</v>
@@ -892,15 +958,18 @@
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2022</v>
       </c>
-      <c r="B16" s="1">
-        <v>1</v>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C16" s="1">
         <v>15</v>
@@ -909,15 +978,18 @@
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2022</v>
       </c>
-      <c r="B17" s="1">
-        <v>1</v>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C17" s="1">
         <v>16</v>
@@ -926,15 +998,18 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2022</v>
       </c>
-      <c r="B18" s="1">
-        <v>1</v>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C18" s="1">
         <v>17</v>
@@ -943,15 +1018,18 @@
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2022</v>
       </c>
-      <c r="B19" s="1">
-        <v>1</v>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C19" s="1">
         <v>18</v>
@@ -960,15 +1038,18 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>2022</v>
       </c>
-      <c r="B20" s="1">
-        <v>1</v>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C20" s="1">
         <v>19</v>
@@ -977,15 +1058,18 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>2022</v>
       </c>
-      <c r="B21" s="1">
-        <v>1</v>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C21" s="1">
         <v>20</v>
@@ -994,10 +1078,13 @@
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>2022</v>
       </c>
@@ -1005,16 +1092,16 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>2022</v>
       </c>
@@ -1022,16 +1109,16 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D23" s="1">
         <v>2</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
@@ -1045,10 +1132,10 @@
         <v>2</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>2022</v>
       </c>
@@ -1062,10 +1149,13 @@
         <v>4</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="G25" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>2022</v>
       </c>
@@ -1073,16 +1163,19 @@
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D26" s="1">
         <v>3</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>2022</v>
       </c>
@@ -1090,16 +1183,19 @@
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D27" s="1">
         <v>1</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>2022</v>
       </c>
@@ -1107,16 +1203,19 @@
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D28" s="1">
         <v>1</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G28" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>2022</v>
       </c>
@@ -1124,16 +1223,19 @@
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="G29" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>2022</v>
       </c>
@@ -1141,16 +1243,19 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="G30" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>2022</v>
       </c>
@@ -1158,16 +1263,19 @@
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D31" s="1">
         <v>2</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="G31" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>2022</v>
       </c>
@@ -1175,16 +1283,19 @@
         <v>1</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="G32" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>2022</v>
       </c>
@@ -1192,16 +1303,19 @@
         <v>1</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D33" s="1">
         <v>1</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="G33" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>2022</v>
       </c>
@@ -1209,16 +1323,19 @@
         <v>1</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D34" s="1">
         <v>2</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="G34" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>2022</v>
       </c>
@@ -1232,10 +1349,13 @@
         <v>5</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="G35" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>2022</v>
       </c>
@@ -1243,16 +1363,19 @@
         <v>2</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D36" s="1">
         <v>1</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="G36" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>2022</v>
       </c>
@@ -1260,16 +1383,19 @@
         <v>2</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D37" s="1">
         <v>4</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="G37" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>2022</v>
       </c>
@@ -1277,16 +1403,19 @@
         <v>2</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D38" s="1">
         <v>1</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="G38" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>2022</v>
       </c>
@@ -1294,16 +1423,19 @@
         <v>2</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D39" s="1">
         <v>2</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="G39" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>2022</v>
       </c>
@@ -1311,16 +1443,19 @@
         <v>2</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D40" s="1">
         <v>2</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="G40" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>2022</v>
       </c>
@@ -1328,16 +1463,19 @@
         <v>2</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D41" s="1">
         <v>2</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="G41" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>2022</v>
       </c>
@@ -1345,16 +1483,19 @@
         <v>2</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D42" s="1">
         <v>4</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="G42" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>2022</v>
       </c>
@@ -1362,16 +1503,19 @@
         <v>2</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D43" s="1">
         <v>2</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+      <c r="G43" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>2022</v>
       </c>
@@ -1379,16 +1523,19 @@
         <v>2</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="G44" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>2022</v>
       </c>
@@ -1396,16 +1543,19 @@
         <v>2</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D45" s="1">
         <v>2</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+      <c r="G45" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>2022</v>
       </c>
@@ -1413,16 +1563,19 @@
         <v>2</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D46" s="1">
         <v>4</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="G46" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>2022</v>
       </c>
@@ -1430,16 +1583,19 @@
         <v>2</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D47" s="1">
         <v>2</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="G47" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>2022</v>
       </c>
@@ -1447,16 +1603,19 @@
         <v>2</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D48" s="1">
         <v>3</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="G48" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>2022</v>
       </c>
@@ -1464,16 +1623,19 @@
         <v>2</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D49" s="1">
         <v>3</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="G49" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>2022</v>
       </c>
@@ -1481,16 +1643,19 @@
         <v>2</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D50" s="1">
         <v>4</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+      <c r="G50" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>2022</v>
       </c>
@@ -1498,16 +1663,19 @@
         <v>2</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D51" s="1">
         <v>4</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+      <c r="G51" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>2022</v>
       </c>
@@ -1515,16 +1683,16 @@
         <v>2</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D52" s="1">
         <v>2</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>2022</v>
       </c>
@@ -1532,16 +1700,16 @@
         <v>2</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D53" s="1">
         <v>3</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>2022</v>
       </c>
@@ -1549,13 +1717,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D54" s="1">
         <v>3</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
